--- a/output/topology_excel/12404.xlsx
+++ b/output/topology_excel/12404.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
